--- a/etf_holdings/2026-09-29_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-29_common_holdings_all.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.77%</t>
+          <t>10.00%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -662,11 +662,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.92%</t>
+          <t>12.78%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3800000</v>
+        <v>4000000</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.32%</t>
+          <t>9.23%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -688,7 +688,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.82%</t>
+          <t>8.77%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>12.81%</t>
+          <t>13.09%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14.90%</t>
+          <t>14.78%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>6.62%</t>
+          <t>6.56%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.71%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>9.16%</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -779,11 +779,11 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>347000</v>
+        <v>349000</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.75%</t>
+          <t>8.91%</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -800,12 +800,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>104.66%</t>
+          <t>106.01%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8.72%</t>
+          <t>8.83%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.26%</t>
+          <t>8.80%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -848,11 +848,11 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>7.23%</t>
+          <t>7.16%</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1080000</v>
+        <v>1130000</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>6.52%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -874,7 +874,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7.51%</t>
+          <t>7.68%</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>7.85%</t>
+          <t>7.45%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -900,7 +900,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3.25%</t>
+          <t>3.32%</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.25%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>6.89%</t>
+          <t>6.54%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>6.19%</t>
+          <t>5.89%</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -965,7 +965,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>6.60%</t>
+          <t>6.70%</t>
         </is>
       </c>
       <c r="AJ3" t="n">
@@ -978,20 +978,20 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>7.06%</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>442000</v>
+        <v>413000</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>74.71%</t>
+          <t>72.72%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>6.23%</t>
+          <t>6.06%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.21%</t>
+          <t>7.06%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.49%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2.54%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1073,11 +1073,11 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>5.84%</t>
         </is>
       </c>
       <c r="R4" t="n">
-        <v>2850000</v>
+        <v>2500000</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.37%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>8.24%</t>
+          <t>8.45%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>5.09%</t>
+          <t>4.97%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.69%</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>158000</v>
+        <v>164000</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.58%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>57.30%</t>
+          <t>56.41%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>4.77%</t>
+          <t>4.70%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.09%</t>
+          <t>8.06%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>8.64%</t>
+          <t>8.57%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.38%</t>
+          <t>3.40%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1246,11 +1246,11 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.08%</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>311000</v>
+        <v>309000</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>4.75%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.94%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.58%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4.06%</t>
+          <t>4.04%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1337,11 +1337,11 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>4.88%</t>
+          <t>4.94%</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>100000</v>
+        <v>101000</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>3.89%</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>55.98%</t>
+          <t>55.96%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4.67%</t>
+          <t>4.66%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
